--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73A759C-4432-4636-BBB9-325EC448999B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD31A747-8840-46EB-8F60-8D730D75AD25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7476" windowHeight="8916" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19008" windowHeight="9060" activeTab="2" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
   <sheets>
     <sheet name="4. évf" sheetId="1" r:id="rId1"/>
@@ -1165,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E74B09-1592-4B2F-8A8F-90DE63FDA08A}">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1474,457 +1474,6 @@
       </c>
       <c r="C28" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15400D6-8F26-4BDF-8F2A-A84DB8BE5864}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
@@ -2325,6 +1874,457 @@
       </c>
       <c r="C35" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD31A747-8840-46EB-8F60-8D730D75AD25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EE3F3C-C06C-4F3E-AED5-1C0CC9836E33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19008" windowHeight="9060" activeTab="2" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
   <sheets>
     <sheet name="4. évf" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="251">
   <si>
     <t>Lecke</t>
   </si>
@@ -698,6 +698,90 @@
   </si>
   <si>
     <t>Mit gondolsz…?</t>
+  </si>
+  <si>
+    <t>4a</t>
+  </si>
+  <si>
+    <t>vet</t>
+  </si>
+  <si>
+    <t>állatorvos</t>
+  </si>
+  <si>
+    <t>big</t>
+  </si>
+  <si>
+    <t>nagy</t>
+  </si>
+  <si>
+    <t>small</t>
+  </si>
+  <si>
+    <t>kicsi</t>
+  </si>
+  <si>
+    <t>tail</t>
+  </si>
+  <si>
+    <t>farok</t>
+  </si>
+  <si>
+    <t>over there ott</t>
+  </si>
+  <si>
+    <t>wing</t>
+  </si>
+  <si>
+    <t>szárny</t>
+  </si>
+  <si>
+    <t>different</t>
+  </si>
+  <si>
+    <t>különböző</t>
+  </si>
+  <si>
+    <t>very much</t>
+  </si>
+  <si>
+    <t>nagyon</t>
+  </si>
+  <si>
+    <t>broken</t>
+  </si>
+  <si>
+    <t>törött</t>
+  </si>
+  <si>
+    <t>next</t>
+  </si>
+  <si>
+    <t>következő</t>
+  </si>
+  <si>
+    <t>enter</t>
+  </si>
+  <si>
+    <t>belép</t>
+  </si>
+  <si>
+    <t>for sure</t>
+  </si>
+  <si>
+    <t>biztosan</t>
+  </si>
+  <si>
+    <t>popular</t>
+  </si>
+  <si>
+    <t>népszerű</t>
+  </si>
+  <si>
+    <t>dr</t>
+  </si>
+  <si>
+    <t>dr (doktor)</t>
   </si>
 </sst>
 </file>
@@ -1165,7 +1249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E74B09-1592-4B2F-8A8F-90DE63FDA08A}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1474,6 +1558,157 @@
       </c>
       <c r="C28" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>223</v>
+      </c>
+      <c r="B29" t="s">
+        <v>224</v>
+      </c>
+      <c r="C29" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B30" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B31" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C32" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B33" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B34" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B36" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B37" t="s">
+        <v>239</v>
+      </c>
+      <c r="C37" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" t="s">
+        <v>241</v>
+      </c>
+      <c r="C38" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B39" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C40" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" t="s">
+        <v>247</v>
+      </c>
+      <c r="C41" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>223</v>
+      </c>
+      <c r="B42" t="s">
+        <v>249</v>
+      </c>
+      <c r="C42" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/data/szavak.xlsx
+++ b/data/szavak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\szószedet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EE3F3C-C06C-4F3E-AED5-1C0CC9836E33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E0BE7B-457A-4EF5-84CB-7681CB94F12F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{E6ED681C-CEEF-4325-8AAC-6357EF08A3E8}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="284">
   <si>
     <t>Lecke</t>
   </si>
@@ -782,6 +782,105 @@
   </si>
   <si>
     <t>dr (doktor)</t>
+  </si>
+  <si>
+    <t>4b</t>
+  </si>
+  <si>
+    <t>old</t>
+  </si>
+  <si>
+    <t>régi</t>
+  </si>
+  <si>
+    <t>party</t>
+  </si>
+  <si>
+    <t>buli</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>súly</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>magasság</t>
+  </si>
+  <si>
+    <t>chubby</t>
+  </si>
+  <si>
+    <t>duci</t>
+  </si>
+  <si>
+    <t>slim</t>
+  </si>
+  <si>
+    <t>karcsú, vékony</t>
+  </si>
+  <si>
+    <t>dark</t>
+  </si>
+  <si>
+    <t>sötét</t>
+  </si>
+  <si>
+    <t>fair</t>
+  </si>
+  <si>
+    <t>világos</t>
+  </si>
+  <si>
+    <t>hair</t>
+  </si>
+  <si>
+    <t>haj</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>hosszú</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>rövid</t>
+  </si>
+  <si>
+    <t>old(= not young)</t>
+  </si>
+  <si>
+    <t>öreg, idős</t>
+  </si>
+  <si>
+    <t>young</t>
+  </si>
+  <si>
+    <t>fiatal</t>
+  </si>
+  <si>
+    <t>tall</t>
+  </si>
+  <si>
+    <t>magas</t>
+  </si>
+  <si>
+    <t>What does he/ she look like?</t>
+  </si>
+  <si>
+    <t>Welldone</t>
+  </si>
+  <si>
+    <t>Ügyes vagy</t>
+  </si>
+  <si>
+    <t>Hogy néz ki</t>
   </si>
 </sst>
 </file>
@@ -1249,8 +1348,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E74B09-1592-4B2F-8A8F-90DE63FDA08A}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1709,6 +1811,182 @@
       </c>
       <c r="C42" t="s">
         <v>250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" t="s">
+        <v>252</v>
+      </c>
+      <c r="C43" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B44" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B45" t="s">
+        <v>256</v>
+      </c>
+      <c r="C45" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B46" t="s">
+        <v>258</v>
+      </c>
+      <c r="C46" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C47" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B48" t="s">
+        <v>262</v>
+      </c>
+      <c r="C48" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B49" t="s">
+        <v>264</v>
+      </c>
+      <c r="C49" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B50" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B51" t="s">
+        <v>268</v>
+      </c>
+      <c r="C51" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B52" t="s">
+        <v>270</v>
+      </c>
+      <c r="C52" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B53" t="s">
+        <v>272</v>
+      </c>
+      <c r="C53" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B54" t="s">
+        <v>274</v>
+      </c>
+      <c r="C54" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B55" t="s">
+        <v>276</v>
+      </c>
+      <c r="C55" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B56" t="s">
+        <v>278</v>
+      </c>
+      <c r="C56" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>251</v>
+      </c>
+      <c r="B57" t="s">
+        <v>280</v>
+      </c>
+      <c r="C57" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B58" t="s">
+        <v>281</v>
+      </c>
+      <c r="C58" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
